--- a/test_cases.xlsx
+++ b/test_cases.xlsx
@@ -10,6 +10,7 @@
   <sheets>
     <sheet name="Тест-кейсы регистрации" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Login UI+E2E" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Search Page" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Тест-кейсы регистрации'!A1:G26</definedName>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="199">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -417,6 +418,27 @@
     <t xml:space="preserve">Примечания</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">TC-10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">Успешный вход с корректными данными (E2E)</t>
   </si>
   <si>
@@ -432,6 +454,27 @@
     <t xml:space="preserve">Пользователь успешно авторизован, переход на главную страницу или дашборд</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">TC-10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">Вход с некорректным паролем (E2E)</t>
   </si>
   <si>
@@ -444,6 +487,27 @@
     <t xml:space="preserve">Отображается сообщение об ошибке авторизации, вход не выполнен</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">TC-10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">Вход с незарегистрированным email (E2E)</t>
   </si>
   <si>
@@ -459,6 +523,27 @@
     <t xml:space="preserve">Показано сообщение об ошибке о неверных учетных данных</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">TC-10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">Попытка входа с пустым email (UI)</t>
   </si>
   <si>
@@ -474,6 +559,27 @@
     <t xml:space="preserve">Кнопка "Login" неактивна или отображается сообщение об обязательном поле email</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">TC-10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">Попытка входа с пустым паролем (UI)</t>
   </si>
   <si>
@@ -486,6 +592,27 @@
     <t xml:space="preserve">Кнопка "Login" неактивна или отображается сообщение об обязательном поле пароль</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">TC-10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">Проверка восстановления пароля (UI)</t>
   </si>
   <si>
@@ -500,6 +627,27 @@
     <t xml:space="preserve">Если ссылка присутствует на странице</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">TC-10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">Отображение полей на странице логина (UI)</t>
   </si>
   <si>
@@ -510,6 +658,27 @@
     <t xml:space="preserve">Все основные поля и кнопка видны на странице</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">TC-10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">Проверка текстового заголовка страницы логина (UI)</t>
   </si>
   <si>
@@ -518,6 +687,161 @@
   </si>
   <si>
     <t xml:space="preserve">Заголовок отображается корректно</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Отображение страницы поиска и списка товаров</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пользователь открыл страницу http://localhost:3000/#/search</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Перейти на страницу http://localhost:3000/#/search
+2. Проверить отображение области поиска
+3. Проверить наличие списка товаров</t>
+  </si>
+  <si>
+    <t xml:space="preserve">На странице отображается поисковая строка и карточки товаров. Пользователь может видеть доступные товары.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Поиск по полному названию товара</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пользователь открыл страницу поиска</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Нажать на иконку поиска
+2. Ввести полный корректный запрос, например "Apple Juice"
+3. Нажать Enter или дождаться фильтрации</t>
+  </si>
+  <si>
+    <t xml:space="preserve">В списке остаются только товары, содержащие "Apple Juice". Остальные товары скрыты.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Поиск по части названия товара</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Открыть поиск
+2. Ввести часть названия, например "juice"
+3. Проверить результат</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Фильтрация работает без учета регистра, отображаются все товары, содержащие слово "juice".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Поиск с пустым значением</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Открыть поиск
+2. Очистить поле поиска
+3. Проверить отображение товаров</t>
+  </si>
+  <si>
+    <t xml:space="preserve">При пустом запросе отображается полный список товаров, без ошибок и без пустого состояния.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Поиск несуществующего товара</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пользователь на странице поиска</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Открыть поиск
+2. Ввести значение, которого нет в каталоге, например "NotARealProduct"
+3. Проверить результат</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Список товаров пустой или отображается сообщение "No results"/"Ничего не найдено". UI остается стабильным.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Поиск без учета регистра</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Вызвать поиск
+2. Ввести "APPLE JUICE" в верхнем регистре
+3. Проверить результат</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Поиск корректно работает без учета регистра, отображается тот же набор товаров, что и для нижнего регистра.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Закрытие и повторное открытие поиска</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Нажать кнопку закрытия поиска
+2. Проверить, что поле поиска закрыто
+3. Открыть поиск повторно
+4. Ввести запрос</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Поиск корректно открывается и закрывается, введенный запрос сохраняется/обновляется без сбоев UI.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Проверка доступности кнопки "Add to Basket" после фильтрации</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Фильтр применен по названию товара</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Выполнить поиск по товару
+2. Проверить доступность кнопки "Add to Basket" у найденного товара
+3. Нажать кнопку</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Товар можно добавить в корзину напрямую из результатов поиска. Корзина обновляется корректно.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Проверка пагинации после применения поиска</t>
+  </si>
+  <si>
+    <t xml:space="preserve">На странице товаров есть несколько страниц</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Открыть поиск
+2. Ввести запрос, который возвращает много товаров
+3. Проверить номера страниц и навигацию</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Поиск корректно работает с пагинацией: результат фильтруется, кнопки "Previous/Next" обновляются в соответствии с количеством найденных товаров.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Поиск по спецсимволам и цифрам</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Ввести строку с цифрами или спецсимволами, например "2020" или ""Permafrost""
+2. Проверить поведение UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Система обрабатывает ввод корректно: либо показывает соответствующие результаты, либо пустой результат без падения страницы.</t>
   </si>
 </sst>
 </file>
@@ -527,7 +851,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -549,6 +873,12 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -593,7 +923,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -606,12 +936,8 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -804,9 +1130,16 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultColWidth="50.3828125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="33.8125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="1" style="1" width="50.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30.31"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="33.81"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="63.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="46.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="12.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12.29"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="8" style="1" width="33.81"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -855,7 +1188,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="99.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
@@ -947,7 +1280,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
         <v>32</v>
       </c>
@@ -1016,7 +1349,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
         <v>44</v>
       </c>
@@ -1269,7 +1602,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
         <v>89</v>
       </c>
@@ -1315,7 +1648,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
         <v>98</v>
       </c>
@@ -1424,173 +1757,453 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="43.62109375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28.96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="34.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="53.2"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="5" style="1" width="43.62"/>
+  </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+    <row r="1" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="n">
+    <row r="2" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="35.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="48.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="46.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="12.83"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="8" style="1" width="8.5"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="F2" s="3"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="n">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="F3" s="3"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="n">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="F4" s="3"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="n">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="F5" s="3"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="n">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="F6" s="3"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="n">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="F8" s="3"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="F9" s="3"/>
+    </row>
+    <row r="2" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>23</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
